--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_03_Full_84_Cau/Day_03_Ngan_Hang_Phan_02_21_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_03_Full_84_Cau/Day_03_Ngan_Hang_Phan_02_21_Cau.xlsx
@@ -645,7 +645,7 @@
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Không chỉ kiểm kiểu mảng; còn phải kiểm schema của từng phần tử.</t>
+          <t>Trước khi thực thi lệnh gọi `book_room`, runtime cần: Kiểm tra tên tool có trong allowlist (a), Từ chối payload vì phần tử không đúng định dạng email (b), và Thêm Observation về lỗi kiểm tra chỉ rõ vị trí trường lỗi `attendees[0]` (c).</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chỉ suy ra cạnh phụ thuộc từ các đầu vào đã được khai báo.</t>
+          <t>Phân tích đồ thị phụ thuộc (DAG): A (`get_user`), B (`get_weather`) và D (`log_request`) không phụ thuộc lẫn nhau nên có thể chạy song song (a); C (`recommend`) nhận đầu vào từ A và B nên bắt buộc phải chờ A và B hoàn tất (b); Chạy C quá sớm sẽ thiếu đầu vào (e).</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Theo dõi luồng điều khiển khi cả hai điều kiện cùng đúng.</t>
+          <t>Lỗi luồng điều khiển là mã kiểm tra `if tool_call: execute(); append();` rồi rơi ngay xuống `if text: return text`, khiến phản hồi tạm 'Calling tool...' bị trả về như câu trả lời cuối cùng cho người dùng trước khi lượt gọi model kế tiếp có cơ hội đọc Observation.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_03_Full_84_Cau/Day_03_Ngan_Hang_Phan_02_21_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_03_Full_84_Cau/Day_03_Ngan_Hang_Phan_02_21_Cau.xlsx
@@ -823,10 +823,22 @@
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đối chiếu từng kết quả với `call_id` và tham số ban đầu.
-Phân tích theo nguyên lý thiết kế: Đối chiếu từng kết quả với `call_id` và tham số ban đầu.</t>
+- Xác định chính xác lỗi hoán đổi call_id (1.0 điểm): Chỉ rõ kết quả thời tiết bị gán sai cho a2 và lịch bị gán sai cho a1.
+- Phân tích hậu quả kỹ thuật và ảo giác nghiệp vụ (1.0 điểm): Vi phạm giao thức API và khiến mô hình trả lời lẫn lộn giữa nhiệt độ và lịch họp.
+- Đề xuất cách sửa tối thiểu chuẩn xác (1.0 điểm): Sử dụng mapping theo khóa `call_id` đích danh thay vì dựa vào thứ tự xuất hiện.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Chỉ ra lỗi trong Trace (State Alignment Inversion Bug):
+- Lỗi hoán đổi mã định danh cuộc gọi (Call ID Mismatch / Misalignment): Hệ thống đã gán ngược Observation thời tiết cho `call_id=a2` (vốn là lệnh gọi lịch `get_calendar(today)`), và gán Observation lịch cho `call_id=a1` (vốn là lệnh gọi thời tiết `get_weather(HN)`).
+2. Hậu quả kỹ thuật và nghiệp vụ nghiêm trọng:
+- Vi phạm giao thức LLM Function Calling: Các nhà cung cấp mô hình lớn (OpenAI, Anthropic, Google) yêu cầu ánh xạ 1-1 chính xác tuyệt đối giữa `tool_call_id` trong tin nhắn yêu cầu của mô hình và `tool_call_id` trong phản hồi của tool. Gán sai id sẽ khiến API trả lỗi 400 Bad Request hoặc khiến mô hình bị 'loạn ngữ cảnh'.
+- Gây ảo giác hoán đổi thông tin (Cross-Domain Hallucination): Mô hình sẽ đọc Observation bị gán nhầm và tin rằng 'Lịch trình chiều nay là 32 độ C, trời nắng' và 'Thời tiết ở Hà Nội là họp giao ban 15h00', dẫn đến câu trả lời cuối cùng bị đảo lộn tai hại.
+3. Cách sửa tối thiểu (Minimal Fix):
+- Ánh xạ theo `call_id` tường minh thay vì dựa vào thứ tự mảng kết quả: Khi nhận kết quả bất đồng bộ từ các tool, lớp điều phối phải dùng `call_id` làm khóa tra cứu (Dictionary Key) để đóng gói `ToolMessage(tool_call_id=res.call_id, content=res.content)`.
+- Cụ thể: Gán kết quả của `get_weather(HN)` cho `call_id=a1`, và gán kết quả của `get_calendar(today)` cho `call_id=a2`.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Tính Toàn vẹn Tham chiếu Trạng thái (State Referential Integrity). Khi thực thi nhiều tool song song (Parallel Tool Execution), thời gian phản hồi của mạng có thể bị xáo trộn. Nếu runtime chỉ đơn thuần đẩy kết quả vào mảng theo thứ tự hoàn thành mà không đối chiếu `call_id`, sự hoán đổi ngữ cảnh sẽ làm sập hoàn toàn khả năng lập luận của LLM.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OpenAI Platform Docs - Parallel Tool Calling Message Structure (https://platform.openai.com/docs/guides/function-calling#parallel-function-calling); Anthropic - Tool Use Protocol &amp; Tool Result ID Matching (https://docs.anthropic.com/en/docs/build-with-claude/tool-use)</t>
         </is>
       </c>
     </row>
@@ -907,10 +919,21 @@
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Chỉ có dữ liệu của một phía thì chưa đủ để chọn phương án tốt hơn.
-Phân tích theo nguyên lý thiết kế: Chỉ có dữ liệu của một phía thì chưa đủ để chọn phương án tốt hơn.</t>
+- Viết phản hồi cuối hợp lệ và minh bạch (1.5 điểm): Cung cấp đầy đủ thông tin chuyến A, công khai sự cố lỗi của chuyến B, và khẳng định chưa thể so sánh.
+- Giải thích chặt chẽ vì sao chưa được kết luận (1.5 điểm): Phân tích logic mệnh đề so sánh 2 ngôi đòi hỏi dữ liệu cả 2 phía, chỉ ra nguy cơ chuyến B có thể tốt hơn.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phản hồi cuối hợp lệ (Valid Evidence-Gated Response):
+"Dựa trên dữ liệu tra cứu hệ thống:
+- Chuyến bay A: Giá vé là 1.850.000 VNĐ, giờ hạ cánh dự kiến là 14h30.
+- Chuyến bay B: Dịch vụ tra cứu dữ liệu chuyến bay B hiện đang gặp sự cố kết nối gián đoạn, do đó hệ thống chưa thể lấy được thông tin giá vé và giờ đến thực tế của chuyến B.
+- Kết luận so sánh: Hệ thống CHƯA THỂ KẾT LUẬN chuyến bay nào tốt hơn về giá và thời gian đến do thiếu dữ liệu đối chứng của chuyến B. Quý khách vui lòng thử lại sau ít phút hoặc để tôi hỗ trợ tra cứu lại chuyến B."
+2. Giải thích vì sao TUYỆT ĐỐI CHƯA ĐƯỢC KẾT LUẬN A TỐT HƠN:
+- Vi phạm nguyên lý đối sánh đầy đủ (Comparative Grounding Incompleteness): Tuyên bố 'A tốt hơn B' là một mệnh đề so sánh quan hệ 2 ngôi ($A &gt; B$). Mệnh đề này chỉ có giá trị logic khi và chỉ khi cả 2 toán tử đều có giá trị xác định. Khi chuyến B chưa có dữ liệu, chuyến B hoàn toàn có thể có giá rẻ hơn (ví dụ 1.200.000 VNĐ) hoặc giờ đến tối ưu hơn.
+- Tránh ngộ nhận 'Có dữ liệu đồng nghĩa với Tốt hơn' (Availability Bias / Hallucinated Superiority): Người dùng có thể bị dẫn dụ chọn chuyến bay A đắt hơn chỉ vì hệ thống vội vã kết luận khi thông tin còn khuyết thiếu.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Chốt chặn Bằng chứng Đầy đủ (Evidence-Gated Completion Boundary). Một trong những điểm yếu lớn nhất của mô hình ngôn ngữ là 'cố chiều lòng người dùng' bằng cách đưa ra câu trả lời dứt khoát ngay cả khi một nhánh dữ liệu đầu vào bị lỗi. Thiết kế có đạo đức yêu cầu Agent phải minh bạch về khoảng trống dữ liệu và kiên quyết từ chối so sánh thiên lệch khi thiếu một vế thông tin.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google PAIR Guidebook - Graceful Failure &amp; Epistemic Transparency (https://pair.withgoogle.com/guidebook/); ISO/IEC 42001 - AI Management System (Trustworthiness &amp; Transparency).</t>
         </is>
       </c>
     </row>
@@ -1181,10 +1204,43 @@
       <c r="K15" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt lỗi tại nơi biết cả `call_id` lẫn tên tool.
-Phân tích theo nguyên lý thiết kế: Bắt lỗi tại nơi biết cả `call_id` lẫn tên tool.</t>
+- Mã giả bắt ngoại lệ tại điểm có call_id và tool_name (1.5 điểm): Khối try-except bắt `TimeoutError`, bọc thành tin nhắn tool có `tool_call_id` thay vì crash app.
+- Trạng thái chuẩn hóa model nhìn thấy ở lượt sau (1.5 điểm): Thể hiện rõ `ToolMessage` chứa JSON thông báo lỗi timeout, gắn với `call_id='c9'`, sẵn sàng cho model suy luận tiếp.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Mã giả bắt lỗi TimeoutError và chuyển thành Observation an toàn:
+```python
+def execute_tool(call_id, tool_name, args):
+    try:
+        # Thực thi lệnh gọi tool với ngưỡng timeout kiểm soát
+        result = registry[tool_name].invoke(args, timeout=5.0)
+        return {
+            "role": "tool",
+            "tool_call_id": call_id,
+            "content": json.dumps({"success": true, "data": result})
+        }
+    except TimeoutError as e:
+        # BẮT LỖI TẠI NƠI BIẾT RÕ CALL_ID VÀ TOOL_NAME, KHÔNG ĐỂ THOÁT RA LÀM CHẾT APP
+        return {
+            "role": "tool",
+            "tool_call_id": call_id,
+            "content": json.dumps({
+                "success": false,
+                "error_type": "TimeoutError",
+                "tool": tool_name,
+                "message": "Hết thời gian chờ phản hồi từ dịch vụ tra cứu đơn hàng sau 5000ms.",
+                "retryable": true
+            })
+        }
+```
+2. Trạng thái mà Model phải nhìn thấy ở lượt tiếp theo (Next-Turn State):
+- Trong lịch sử tin nhắn truyền cho model, lượt trước không bị đứt đoạn mà có đầy đủ cặp Action - Observation:
+  + Tin nhắn trợ lý trước: `AIMessage(tool_calls=[{'id': 'c9', 'name': 'search_orders', 'args': {...}}])`
+  + Tin nhắn công cụ kế tiếp: `ToolMessage(tool_call_id='c9', content='{"success": false, "error_type": "TimeoutError", "tool": "search_orders", "message": "Hết thời gian chờ phản hồi từ dịch vụ tra cứu đơn hàng sau 5000ms.", "retryable": true}')`
+- Nhờ cấu trúc này, mô hình nhận thức được lệnh gọi `c9` đã kết thúc trong thất bại do mạng và có thể tự quyết định: thử lại (retry) hoặc thông báo lỗi cho người dùng.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Mã hóa Lỗi thành Nhận thức (Error-as-Observation Pattern). Nếu ngoại lệ hạ tầng (như `TimeoutError`) không được bắt tại ranh giới thực thi mà để thoát ra ngoài, tiến trình chạy nền sẽ sụp đổ (Process Crash). Bằng cách chuyển đổi exception thành một `ToolMessage` hợp lệ liên kết với `call_id`, hệ thống chuyển giao lỗi hạ tầng thành tri thức quan sát được để mô hình tiếp tục vòng lặp tự phục hồi.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LangChain / LangGraph Docs - Tool Error Handling &amp; ToolMessage Patterns (https://python.langchain.com/docs/how_to/tools_error_handling/); Anthropic Claude Tool Use Guide - Handling Errors.</t>
         </is>
       </c>
     </row>
@@ -1265,10 +1321,21 @@
       <c r="K17" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Không để bất kỳ bước phân tích nào thực thi mã lấy từ văn bản do model sinh ra.
-Phân tích theo nguyên lý thiết kế: Không để bất kỳ bước phân tích nào thực thi mã lấy từ văn bản do model sinh ra.</t>
+- Nêu đủ 3 vấn đề kỹ thuật và bảo mật (1.5 điểm): Chỉ ra lỗ hổng RCE qua `eval()`, lỗi regex một dòng cắt cụt dữ liệu, và lỗi vỡ định dạng khi model thêm khoảng trắng/text thừa.
+- Thiết kế quy trình phân tích thay thế an toàn (1.5 điểm): Đề xuất regex chặt chẽ, thay thế `eval` bằng `json.loads` hoặc `ast.literal_eval`, và kiểm tra qua allowlist.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân tích 3 lỗi và vấn đề bảo mật nghiêm trọng của regex `Action:(.*)` và `eval(action_input)`:
+- Lỗ hổng Thực thi Mã Tùy ý Nghiêm trọng (Remote Code Execution - RCE via `eval`): `eval()` sẽ trực tiếp thông dịch và thực thi bất kỳ mã Python nào nằm trong chuỗi `action_input`. Kẻ tấn công có thể tiêm mã độc qua prompt injection (ví dụ `Action: bash; action_input: __import__('os').system('rm -rf /')` hoặc đọc file bí mật) để chiếm quyền điều khiển toàn bộ máy chủ.
+- Lỗi sai định dạng đa dòng (Multiline Parsing Fragility): Biểu thức chính quy `Action:(.*)` theo mặc định dừng lại ở ký tự xuống dòng đầu tiên (`\n`). Nếu tham số đầu vào là văn bản dài có xuống dòng, regex sẽ cắt cụt dữ liệu, gây lỗi cú pháp.
+- Lỗi nhạy cảm khoảng trắng và không dung thứ sai sót (Lack of Format Robustness): Model có thể sinh ra `Action :`, `Action:`, hoặc viết thêm phần suy nghĩ trước khi gọi action. Regex cứng nhắc sẽ không trích xuất được hoặc bắt nhầm văn bản tự do.
+2. Thiết kế quy trình phân tích tối thiểu an toàn hơn cho Text-ReAct (Safe Parsing Pipeline):
+- Bước 1: Chuẩn hóa và Trích xuất phân đoạn (Sanitized Regex Extraction): Dùng biểu thức chính quy chặt chẽ bắt khối hành động có cờ đa dòng, ví dụ: `(?s)Action:\s*([a-zA-Z0-9_]+)\s*Action Input:\s*({.*}|\[.*\]|".*")`.
+- Bước 2: Phân tích cú pháp an toàn Tuyệt đối KHÔNG DÙNG `eval()` (Safe Deserialization): Sử dụng `json.loads()` hoặc `ast.literal_eval()` để chuyển đổi `action_input` thành đối tượng dữ liệu. Bắt ngoại lệ `json.JSONDecodeError` nếu model sinh cú pháp hỏng.
+- Bước 3: Kiểm tra tính hợp lệ qua Registry Allowlist: Xác thực tên Action nằm trong danh sách hàm cho phép trước khi điều phối.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Phòng chống Lỗ hổng Injection trong Bộ phân tích Cú pháp (Parser Hardening &amp; Code Injection Defense). Việc sử dụng `eval()` trên đầu ra của mô hình ngôn ngữ là một sai lầm bảo mật chết người (CWE-95: Eval Injection). Đầu ra của LLM phải luôn được xem là nguồn dữ liệu không đáng tin cậy (Untrusted Input) và chỉ được phân tích bằng các bộ giải mã dữ liệu thụ động như JSON parser.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+CWE-95: Improper Neutralization of Directives in Dynamically Evaluated Code ('Eval Injection') (https://cwe.mitre.org/data/definitions/95.html); OWASP Top 10 for LLMs - LLM02: Insecure Output Handling.</t>
         </is>
       </c>
     </row>
@@ -1347,10 +1414,35 @@
       <c r="K19" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đặt các trường riêng của từng SDK phía sau một lớp chuyển đổi ở ranh giới.
-Phân tích theo nguyên lý thiết kế: Đặt các trường riêng của từng SDK phía sau một lớp chuyển đổi ở ranh giới.</t>
+- Thiết kế đầu ra chuẩn hóa trung lập (1.0 điểm): Định nghĩa rõ cấu trúc gồm `call_id`, `tool_name`, `arguments` (dạng dict) và `raw_error`.
+- Thiết kế đủ 4 trường hợp kiểm thử bao quát (2.0 điểm): Bao gồm input Provider A, parallel calls Provider B, lỗi JSON cú pháp và trường hợp không có tool call.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế đầu ra chuẩn hóa của lớp chuyển đổi (Unified Normalized Adapter Output):
+Lớp chuyển đổi ở ranh giới (Boundary Adapter) ánh xạ cấu trúc riêng của các nhà cung cấp SDK về một cấu trúc dữ liệu trung lập nội bộ (Canonical Tool Call Schema):
+```python
+class NormalizedToolCall:
+    call_id: str          # Mã định danh duy nhất của lệnh gọi tool
+    tool_name: str        # Tên công cụ chuẩn hóa
+    arguments: dict       # Từ điển tham số đã được giải mã JSON an toàn
+    raw_error: str | None # Lưu lỗi nếu chuỗi tham số không parse được
+```
+2. Bốn dữ liệu kiểm thử bắt buộc (Test Cases for Adapter Layer):
+- Test Case 1: Chuyển đổi thành công từ Nhà cung cấp A (Single Tool Call from Provider A)
+  + Input: `{"kind": "function", "function": {"name": "get_weather", "json_arguments": "{\"city\": \"Hanoi\"}"}, "id": "call_1"}`
+  + Expected Output: `NormalizedToolCall(call_id='call_1', tool_name='get_weather', arguments={'city': 'Hanoi'}, raw_error=None)`.
+- Test Case 2: Chuyển đổi thành công nhiều lệnh gọi song song từ Nhà cung cấp B (Parallel Calls from Provider B)
+  + Input: `{"tool_calls": [{"fn": "read_doc", "args": {"id": 10}}, {"fn": "notify", "args": {"msg": "done"}}], "id_prefix": "call_2"}`
+  + Expected Output: Danh sách 2 đối tượng `NormalizedToolCall` với `tool_name` và `arguments` tương ứng.
+- Test Case 3: Xử lý tham số JSON bị lỗi cú pháp từ mô hình (Malformed JSON Arguments)
+  + Input từ Provider A: `json_arguments: "{\"city\": \"Hanoi\""` (thiếu ngoặc đóng).
+  + Expected Output: `NormalizedToolCall` ghi nhận `arguments={}`, `raw_error='JSONDecodeError'` để vòng lặp trả Observation lỗi về cho model mà không làm sập adapter.
+- Test Case 4: Không có lệnh gọi tool nào (Direct Final Response / No Tool Invoked)
+  + Input: Phản hồi thuần văn bản không có trường `function` hay `tool_calls`.
+  + Expected Output: Trả về danh sách rỗng `[]`, báo hiệu vòng lặp chuyển thẳng sang hoàn tất tác vụ.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Mẫu hình Bộ chuyển đổi Ranh giới (Adapter Pattern &amp; Hexagonal Architecture). Sự phân mảnh SDK giữa các nhà cung cấp mô hình (OpenAI function calling, Anthropic tool use, Gemini function calling) dễ làm ô nhiễm mã nguồn vòng lặp Agent. Đặt lớp Adapter ở ranh giới giúp vòng lặp hoàn toàn độc lập với chi tiết giao thức của từng hãng, dễ dàng chuyển đổi nhà cung cấp mô hình mà không cần viết lại một dòng mã logic nào.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Gamma, E., et al. Design Patterns: Elements of Reusable Object-Oriented Software (Adapter Pattern); LangChain BaseTool &amp; ToolCall Specification (https://python.langchain.com/docs/concepts/tools/)</t>
         </is>
       </c>
     </row>
@@ -1425,10 +1517,22 @@
       <c r="K21" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Nêu cả cơ chế kiểm soát hiện tại và bằng chứng cho thấy cần đổi cơ chế.
-Phân tích theo nguyên lý thiết kế: Nêu cả cơ chế kiểm soát hiện tại và bằng chứng cho thấy cần đổi cơ chế.</t>
+- Chọn đúng cơ chế Text-ReAct có phân tách (1.0 điểm): Giải thích rõ mô hình cục bộ chỉ sinh text nên cần prompt Text-ReAct kèm thẻ cú pháp để gỡ lỗi offline.
+- Nêu ít nhất 2 biện pháp bảo vệ vững chắc (1.0 điểm): Parser an toàn không eval kèm phản hồi sửa lỗi, và bộ ngắt mạch chống lặp cú pháp sai.
+- Điều kiện bằng chứng chuyển đổi rõ ràng (1.0 điểm): Mô hình mới hỗ trợ native tool và tỷ lệ lỗi cú pháp thực nghiệm giảm dưới ngưỡng định lượng (&lt; 1%).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Lựa chọn cơ chế phù hợp cho mô hình cục bộ ngoại tuyến:
+- LỰA CHỌN BẮT BUỘC: CƠ CHẾ TEXT-REACT DỰA TRÊN PROMPT VÀ BỘ PHÂN TÍCH CÚ PHÁP ĐỘC LẬP (Prompt-driven Text-ReAct with Structured Tag / JSON Delimiter Parsing).
+- Lý do: Mô hình cục bộ (Local SLM / LLM) không hỗ trợ API function calling nguyên bản của nền tảng và chạy offline. Cơ chế sinh văn bản chứa thẻ định dạng rõ ràng (ví dụ `&lt;tool_call&gt;{"name": ..., "args": ...}&lt;/tool_call&gt;`) cho phép kiểm soát 100% việc gỡ lỗi bộ parser trên máy chủ cục bộ mà không phụ thuộc hạ tầng ngoài.
+2. Ít nhất hai biện pháp bảo vệ bắt buộc (Defensive Safeguards):
+- Biện pháp 1 - Trích xuất không dùng `eval()` kèm Bộ phân tích lỗi cú pháp (Strict JSON Parser with Schema Guard): Bắt buộc dùng `json.loads` trích xuất nội dung trong thẻ. Nếu model sinh JSON thiếu ngoặc hoặc thừa ký tự, parser bắt `JSONDecodeError` và tự động trả về Observation: 'Cú pháp gọi tool không hợp lệ, vui lòng chỉ sinh đúng định dạng JSON chuẩn'.
+- Biện pháp 2 - Bộ ngắt mạch lặp không tiến triển (Loop Non-progress Circuit Breaker): Mô hình cục bộ thường xuyên bị kẹt trong vòng lặp sinh lại cùng một cú pháp văn bản sai. Đặt ngưỡng tối đa 3 lần parse lỗi liên tiếp để ngắt vòng lặp khẩn cấp và chuyển sang phản hồi an toàn.
+3. Điều kiện bằng chứng để chuyển sang cơ chế Native Function Calling trong tương lai:
+- Khi thỏa mãn đồng thời 2 điều kiện: (1) Mô hình cục bộ được nâng cấp lên trọng số mới có fine-tune hỗ trợ native function calling (như Llama-3-Instruct hoặc Qwen-2.5); và (2) Dữ liệu đo kiểm đối sánh thực nghiệm trên tập 100 test case cho thấy tỷ lệ lỗi cú pháp (Syntax Parse Error Rate) của cơ chế Native giảm xuống dưới 1% so với Text-ReAct.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Lựa chọn Cơ chế Điều phối Phù hợp Ràng buộc Phần cứng (Execution Mechanism Trade-off). Khi vận hành ngoại tuyến với mô hình mã nguồn mở cỡ nhỏ, cơ chế Text-ReAct phân tách rõ ràng luồng sinh văn bản và luồng parse. Việc chuyển đổi cơ chế trong tương lai không được dựa vào cảm tính mà phải dựa trên bằng chứng định lượng về độ tin cậy cú pháp.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Yao, S., et al. (2022). ReAct: Synergizing Reasoning and Acting in Language Models; Hugging Face TGI / vLLM - Guidance on Tool Calling with Local Models (https://huggingface.co/docs/transformers/main/en/main_classes/text_generation)</t>
         </is>
       </c>
     </row>
@@ -1457,10 +1561,28 @@
       <c r="K22" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Viết 'ai–làm gì–dùng gì–trong điều kiện nào'.
-Phân tích theo nguyên lý thiết kế: Viết 'ai–làm gì–dùng gì–trong điều kiện nào'.</t>
+- Nêu rõ vai trò và định danh (Ai - 1.0 điểm): Xác định đúng Trợ lý hỗ trợ CNTT L1 và phạm vi nội bộ.
+- Nêu rõ nhiệm vụ và công cụ tương ứng (Làm gì, Dùng gì - 1.0 điểm): Gắn `lookup_policy` cho tra cứu và `create_ticket` cho sự cố.
+- Điều kiện thực thi công cụ chỉ đọc (1.0 điểm): Yêu cầu bắt buộc tra cứu chính sách trước khi trả lời, cấm tự suy diễn.
+- Điều kiện thực thi công cụ tác động phụ (1.0 điểm): Đặt cổng xác nhận người dùng tường minh và đủ 4 tham số trước khi gọi `create_ticket`.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế đặc tả Hợp đồng Vai trò - Khả năng (Role &amp; Capability Contract) cho Agent Hỗ trợ CNTT theo mẫu 'Ai - Làm gì - Dùng gì - Trong điều kiện nào':
+```markdown
+# HỢP ĐỒNG NĂNG LỰC VÀ VAI TRÒ (IT SUPPORT AGENT CONTRACT)
+## 1. Định danh và Phạm vi Vai trò (Who - Identity &amp; Scope)
+- Bạn là Trợ lý Hỗ trợ Kỹ thuật CNTT Nội bộ Cấp 1 (L1 IT Support Agent). Nhiệm vụ duy nhất của bạn là giải đáp chính sách kỹ thuật và tiếp nhận yêu cầu xử lý sự cố CNTT cho nhân viên công ty.
+## 2. Năng lực và Công cụ được cấp quyền (What &amp; Tools - Capabilities)
+- Công cụ Chỉ đọc `lookup_policy(query)`: Dùng để tra cứu các quy định bảo mật, chính sách cấp phát thiết bị và quy trình kỹ thuật nội bộ.
+- Công cụ Có Tác động phụ `create_ticket(title, description, priority, category)`: Dùng để khởi tạo phiếu yêu cầu hỗ trợ mới trên hệ thống Service Desk khi người dùng gặp sự cố không thể tự khắc phục.
+## 3. Điều kiện Thực thi Bắt buộc (Conditions &amp; Boundary Rules)
+- Điều kiện 1 (Tra cứu trước khi hành động): Đối với mọi câu hỏi liên quan đến quy định, bạn bắt buộc phải gọi `lookup_policy` để lấy điều khoản chính xác. Tuyệt đối không tự suy diễn chính sách từ trí nhớ nội tại.
+- Điều kiện 2 (Nguyên tắc Cổng Xác nhận trước Tác động phụ): Bạn CHỈ ĐƯỢC PHÉP gọi `create_ticket` khi thỏa mãn đồng thời: (a) Đã thu thập đủ 4 tham số hợp lệ (tiêu đề, mô tả chi tiết lỗi, độ ưu tiên, danh mục sự cố); và (b) Đã hiển thị bản tóm tắt nội dung phiếu và nhận được sự ĐỒNG Ý XÁC NHẬN TƯỜNG MINH từ người dùng.
+- Điều kiện 3 (Ranh giới cấm vượt quyền): Tuyệt đối không hứa hẹn thời gian xử lý ngoài SLA, không can thiệp vào cơ sở dữ liệu hệ thống, và không thực hiện bất kỳ hành động nào ngoài 2 công cụ được cấp quyền ở trên.
+```
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Hợp đồng Năng lực Tường minh trong Prompt (Prompt-Level Capability Contract). Một chỉ dẫn hệ thống hiệu quả không được viết mơ hồ 'hãy làm người giúp việc tốt'. Việc định nghĩa rạch ròi danh tính, công cụ được cấp quyền, điều kiện tiên quyết (Preconditions) và ranh giới cấm (Prohibitions) tạo ra khuôn viên hành vi chuẩn tắc, ngăn chặn việc agent tự ý thực thi các tác động phụ khi chưa có sự đồng thuận.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Anthropic - Building Effective Agents (System Prompts for Tool Use) (https://www.anthropic.com/research/building-effective-agents); Google Cloud Vertex AI - Agent System Instructions &amp; Constraints.</t>
         </is>
       </c>
     </row>
@@ -1489,10 +1611,30 @@
       <c r="K23" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Một câu trong prompt không thể thay thế quyền thực thi.
-Phân tích theo nguyên lý thiết kế: Một câu trong prompt không thể thay thế quyền thực thi.</t>
+- Viết lại đặc tả vai trò-nhiệm vụ-công cụ cụ thể (1.5 điểm): Thay thế câu chung chung bằng định danh trợ lý phòng khám, phân định rõ công cụ đọc (`read_appointment`) và công cụ ghi (`reschedule_appointment`) kèm luồng xác nhận.
+- Phân định rõ ràng phần runtime bắt buộc thực thi (1.5 điểm): Khẳng định prompt không thay thế được quyền hạn, nêu rõ runtime phải có cổng chặn kiểm tra confirmation token và xác thực quyền sở hữu lịch hẹn.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Viết lại đặc tả Vai trò – Nhiệm vụ – Khả năng trong Prompt:
+```markdown
+# VAI TRÒ: Trợ lý Điều phối Lịch khám Bệnh viện (Clinic Appointment Assistant).
+# NHIỆM VỤ: Hỗ trợ bệnh nhân tra cứu lịch khám đã đăng ký và đổi sang khung giờ mới khả dụng.
+# KHẢ NĂNG &amp; CÔNG CỤ ĐƯỢC PHÉP:
+1. `read_appointment(patient_id, appointment_id)`: Dùng để xem chi tiết lịch hẹn hiện tại (chỉ đọc, không gây tác động phụ).
+2. `reschedule_appointment(appointment_id, new_datetime, reason)`: Dùng để cập nhật lịch khám sang giờ mới (tác động phụ thay đổi dữ liệu).
+# NGUYÊN TẮC HÀNH VI:
+- Bước 1: Luôn gọi `read_appointment` để xác thực lịch hẹn cũ trước khi bàn về việc đổi lịch.
+- Bước 2: Khi người dùng chọn giờ mới, phải hiển thị rõ thông tin lịch cũ vs lịch mới và hỏi xác nhận: 'Bạn có chắc chắn muốn đổi sang khung giờ [giờ mới] không?'.
+- Bước 3: Chỉ phát lệnh gọi `reschedule_appointment` sau khi người dùng trả lời đồng ý.
+```
+2. Phần BẮT BUỘC PHẢI DO RUNTIME THỰC THI RIÊNG (Runtime Authorization Boundary):
+- Một câu dặn trong Prompt 'hãy hỏi xác nhận' KHÔNG THỂ thay thế cơ chế kiểm soát quyền thực thi ở tầng Runtime (Prompt is not a security boundary).
+- Cơ chế Runtime bắt buộc phải cài đặt độc lập:
+  + Cổng Chặn Thực thi (Execution Gate / Interceptor): Khi model phát lệnh gọi `reschedule_appointment`, runtime PHẢI TẠM DỪNG tiến trình và kiểm tra xem trong phiên làm việc đã có sự kiện cờ `USER_CONFIRMATION_TOKEN = TRUE` hay chưa.
+  + Kiểm tra Quyền Hạn (Authorization &amp; Authentication Check): Runtime xác minh danh tính người gửi yêu cầu có đúng là chủ sở hữu của `patient_id` hay không trước khi gửi lệnh vào cơ sở dữ liệu.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: 'Prompt Không Phải Là Hàng Rào Bảo Mật' (Prompt is Not a Security Boundary). Chỉ dẫn trong prompt đóng vai trò hướng dẫn mô hình ứng xử (Guidance), nhưng mô hình ngôn ngữ luôn có xác suất bất tuân quy tắc do ảo giác hoặc do prompt injection từ người dùng. Các thao tác thay đổi dữ liệu quan trọng bắt buộc phải có cổng kiểm soát cứng (Hard Policy Gate) tại lớp runtime nằm ngoài tầm với của LLM.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OWASP Top 10 for LLMs - LLM01: Prompt Injection &amp; Insecure Output Handling (https://owasp.org/www-project-top-10-for-large-language-model-applications/); Saltzer, J. H., &amp; Schroeder, M. D. (1975). The Protection of Information in Computer Systems (https://web.mit.edu/Saltzer/www/publications/protection/index.html).</t>
         </is>
       </c>
     </row>
